--- a/pet_stats.xlsx
+++ b/pet_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E166D563-A4A3-4996-BC14-CA9ED72EE759}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD29EC0-E761-4530-B20F-CFAFA937678A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">pet_stats!$A$1:$V$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">pet_stats!$A$1:$V$810</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="862">
   <si>
     <t>hp</t>
   </si>
@@ -2673,6 +2673,10 @@
   </si>
   <si>
     <t>공룡알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>샤르체류알</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -11492,38 +11496,44 @@
       <c r="A183" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B183" s="6"/>
+      <c r="B183" s="6">
+        <v>71</v>
+      </c>
       <c r="C183" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D183" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E183" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F183" s="11">
-        <v>13.587</v>
+        <v>11.81</v>
       </c>
       <c r="G183" s="11">
-        <v>2.2440000000000002</v>
+        <v>2.89</v>
       </c>
       <c r="H183" s="11">
-        <v>1.49</v>
+        <v>1.413</v>
       </c>
       <c r="I183" s="11">
-        <v>1.3340000000000001</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="J183" s="6">
         <v>1</v>
       </c>
-      <c r="K183" s="6"/>
+      <c r="K183" s="6" t="s">
+        <v>801</v>
+      </c>
       <c r="L183" s="7">
         <f t="shared" si="2"/>
-        <v>5.0679999999999996</v>
+        <v>5.6150000000000002</v>
       </c>
       <c r="M183" s="8"/>
-      <c r="N183" s="8"/>
+      <c r="N183" s="8" t="s">
+        <v>861</v>
+      </c>
       <c r="O183" s="8"/>
       <c r="P183" s="9"/>
     </row>
@@ -29629,38 +29639,44 @@
       <c r="A596" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B596" s="6"/>
+      <c r="B596" s="6">
+        <v>57</v>
+      </c>
       <c r="C596" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D596" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E596" s="6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F596" s="6">
-        <v>9.766</v>
+        <v>10.68</v>
       </c>
       <c r="G596" s="6">
-        <v>2.2890000000000001</v>
+        <v>3.03</v>
       </c>
       <c r="H596" s="6">
-        <v>1.141</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I596" s="6">
-        <v>1.952</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="J596" s="6">
         <v>1</v>
       </c>
-      <c r="K596" s="6"/>
+      <c r="K596" s="6" t="s">
+        <v>801</v>
+      </c>
       <c r="L596" s="7">
         <f t="shared" si="9"/>
-        <v>5.3819999999999997</v>
+        <v>6.370000000000001</v>
       </c>
       <c r="M596" s="8"/>
-      <c r="N596" s="8"/>
+      <c r="N596" s="8" t="s">
+        <v>861</v>
+      </c>
       <c r="O596" s="8"/>
       <c r="P596" s="9"/>
     </row>
@@ -30235,24 +30251,26 @@
       <c r="A610" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B610" s="6"/>
+      <c r="B610" s="6">
+        <v>81</v>
+      </c>
       <c r="C610" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D610" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E610" s="6">
         <v>1</v>
       </c>
       <c r="F610" s="6">
-        <v>12.965999999999999</v>
+        <v>15.98</v>
       </c>
       <c r="G610" s="6">
-        <v>2.282</v>
+        <v>2.21</v>
       </c>
       <c r="H610" s="6">
-        <v>2.7490000000000001</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="I610" s="6">
         <v>0.35799999999999998</v>
@@ -30263,10 +30281,12 @@
       <c r="K610" s="6"/>
       <c r="L610" s="7">
         <f t="shared" si="9"/>
-        <v>5.3890000000000002</v>
+        <v>5.0579999999999998</v>
       </c>
       <c r="M610" s="8"/>
-      <c r="N610" s="8"/>
+      <c r="N610" s="8" t="s">
+        <v>861</v>
+      </c>
       <c r="O610" s="8"/>
       <c r="P610" s="9"/>
     </row>
@@ -33068,40 +33088,44 @@
       <c r="A675" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B675" s="6"/>
+      <c r="B675" s="6">
+        <v>63</v>
+      </c>
       <c r="C675" s="6">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D675" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E675" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F675" s="6">
         <v>9.859</v>
       </c>
       <c r="G675" s="6">
-        <v>2.613</v>
+        <v>3.12</v>
       </c>
       <c r="H675" s="6">
-        <v>1.304</v>
+        <v>1.413</v>
       </c>
       <c r="I675" s="6">
-        <v>1.522</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="J675" s="6">
         <v>1</v>
       </c>
       <c r="K675" s="6" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L675" s="7">
         <f t="shared" si="10"/>
-        <v>5.4390000000000001</v>
+        <v>5.9110000000000005</v>
       </c>
       <c r="M675" s="8"/>
-      <c r="N675" s="8"/>
+      <c r="N675" s="8" t="s">
+        <v>861</v>
+      </c>
       <c r="O675" s="8"/>
       <c r="P675" s="9"/>
     </row>
@@ -38975,7 +38999,7 @@
       <c r="P810" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V1" xr:uid="{B798D69C-EFDD-4E81-84AB-7BD632F26B82}"/>
+  <autoFilter ref="A1:V810" xr:uid="{B798D69C-EFDD-4E81-84AB-7BD632F26B82}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pet_stats.xlsx
+++ b/pet_stats.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD29EC0-E761-4530-B20F-CFAFA937678A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B833C553-84EC-459F-AB06-E4BD90D11789}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pet_stats" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">pet_stats!$A$1:$V$810</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">pet_stats!$A$1:$V$813</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="866">
   <si>
     <t>hp</t>
   </si>
@@ -2677,6 +2677,22 @@
   </si>
   <si>
     <t>샤르체류알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥룡.gif</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>불지옥드래곤.gif</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥얼음드래곤.gif</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신수알</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3207,7 +3223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V810"/>
+  <dimension ref="A1:V813"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -37250,7 +37266,7 @@
       </c>
       <c r="K770" s="6"/>
       <c r="L770" s="7">
-        <f t="shared" ref="L770:L810" si="12">SUM(G770:I770)</f>
+        <f t="shared" ref="L770:L813" si="12">SUM(G770:I770)</f>
         <v>5.6459999999999999</v>
       </c>
       <c r="M770" s="8"/>
@@ -38998,8 +39014,141 @@
       <c r="O810" s="8"/>
       <c r="P810" s="9"/>
     </row>
+    <row r="811" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A811" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="B811" s="6">
+        <v>80</v>
+      </c>
+      <c r="C811" s="6">
+        <v>17</v>
+      </c>
+      <c r="D811" s="6">
+        <v>15</v>
+      </c>
+      <c r="E811" s="6">
+        <v>4</v>
+      </c>
+      <c r="F811" s="6">
+        <v>15.897</v>
+      </c>
+      <c r="G811" s="6">
+        <v>2.3980000000000001</v>
+      </c>
+      <c r="H811" s="6">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="I811" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="J811" s="6">
+        <v>1</v>
+      </c>
+      <c r="K811" s="6"/>
+      <c r="L811" s="7">
+        <f t="shared" si="12"/>
+        <v>5.0410000000000004</v>
+      </c>
+      <c r="M811" s="8"/>
+      <c r="N811" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="O811" s="8"/>
+      <c r="P811" s="9"/>
+    </row>
+    <row r="812" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A812" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="B812" s="6">
+        <v>72</v>
+      </c>
+      <c r="C812" s="6">
+        <v>19</v>
+      </c>
+      <c r="D812" s="6">
+        <v>9</v>
+      </c>
+      <c r="E812" s="6">
+        <v>16</v>
+      </c>
+      <c r="F812" s="6">
+        <v>10.122999999999999</v>
+      </c>
+      <c r="G812" s="6">
+        <v>2.734</v>
+      </c>
+      <c r="H812" s="6">
+        <v>1.6319999999999999</v>
+      </c>
+      <c r="I812" s="6">
+        <v>1.7230000000000001</v>
+      </c>
+      <c r="J812" s="6">
+        <v>1</v>
+      </c>
+      <c r="K812" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="L812" s="7">
+        <f t="shared" si="12"/>
+        <v>6.0889999999999995</v>
+      </c>
+      <c r="M812" s="8"/>
+      <c r="N812" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="O812" s="8"/>
+      <c r="P812" s="9"/>
+    </row>
+    <row r="813" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A813" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="B813" s="6">
+        <v>56</v>
+      </c>
+      <c r="C813" s="6">
+        <v>19</v>
+      </c>
+      <c r="D813" s="6">
+        <v>9</v>
+      </c>
+      <c r="E813" s="6">
+        <v>17</v>
+      </c>
+      <c r="F813" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="G813" s="6">
+        <v>2.698</v>
+      </c>
+      <c r="H813" s="6">
+        <v>1.7130000000000001</v>
+      </c>
+      <c r="I813" s="6">
+        <v>1.4320999999999999</v>
+      </c>
+      <c r="J813" s="6">
+        <v>1</v>
+      </c>
+      <c r="K813" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="L813" s="7">
+        <f t="shared" si="12"/>
+        <v>5.8430999999999997</v>
+      </c>
+      <c r="M813" s="8"/>
+      <c r="N813" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="O813" s="8"/>
+      <c r="P813" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V810" xr:uid="{B798D69C-EFDD-4E81-84AB-7BD632F26B82}"/>
+  <autoFilter ref="A1:V813" xr:uid="{B798D69C-EFDD-4E81-84AB-7BD632F26B82}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
